--- a/data/chinese/P2T3_Chapter12.xlsx
+++ b/data/chinese/P2T3_Chapter12.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/simonlam/My Files/Moons/單詞複習網素材/Chinese/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05B66D6E-ED07-3C46-9DA2-2489F399EBBB}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A86BC817-C77C-6C44-B8DB-715BEFE60267}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25600" yWindow="460" windowWidth="38400" windowHeight="21140" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="25600" yWindow="460" windowWidth="38400" windowHeight="21140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="必懂寫" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="40">
   <si>
     <t>生字</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -150,6 +150,10 @@
   </si>
   <si>
     <t>媽媽在廚房煮食美味晚餐。</t>
+  </si>
+  <si>
+    <t>--</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -236,7 +240,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -257,6 +261,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -573,10 +580,18 @@
       <c r="K1" s="1"/>
     </row>
     <row r="2" spans="1:11" ht="27">
-      <c r="A2" s="3"/>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
+      <c r="A2" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="D2" s="7">
+        <v>1</v>
+      </c>
       <c r="E2" s="5"/>
     </row>
     <row r="3" spans="1:11" ht="27">

--- a/data/chinese/P2T3_Chapter12.xlsx
+++ b/data/chinese/P2T3_Chapter12.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/simonlam/My Files/Moons/單詞複習網素材/Chinese/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A86BC817-C77C-6C44-B8DB-715BEFE60267}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A654AB4-7D58-684C-BE42-69BCB83AE985}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25600" yWindow="460" windowWidth="38400" windowHeight="21140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="25600" yWindow="460" windowWidth="38400" windowHeight="21140" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="必懂寫" sheetId="1" r:id="rId1"/>
@@ -152,7 +152,7 @@
     <t>媽媽在廚房煮食美味晚餐。</t>
   </si>
   <si>
-    <t>--</t>
+    <t>沒有必懂寫生字</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -918,7 +918,7 @@
         <v>17</v>
       </c>
       <c r="D5" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E5" s="5"/>
     </row>
@@ -963,7 +963,7 @@
         <v>26</v>
       </c>
       <c r="D8" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E8" s="5"/>
     </row>
@@ -978,7 +978,7 @@
         <v>29</v>
       </c>
       <c r="D9" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E9" s="5"/>
     </row>
@@ -1008,7 +1008,7 @@
         <v>35</v>
       </c>
       <c r="D11" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E11" s="5"/>
     </row>
@@ -1023,7 +1023,7 @@
         <v>38</v>
       </c>
       <c r="D12" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E12" s="5"/>
     </row>
